--- a/Ministry_of_Energy_and_Water.xlsx
+++ b/Ministry_of_Energy_and_Water.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4285,6 +4285,392 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | بيان صادر عن مجلس إدارة مؤسسة كهرباء لبنان</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101220/%D8%A8%D9%8A%D8%A7%D9%86-%D8%B5%D8%A7%D8%AF%D8%B1-%D8%B9%D9%86-%D9%85%D8%AC%D9%84%D8%B3-%D8%A5%D8%AF%D8%A7%D8%B1%D8%A9-%D9%85%D8%A4%D8%B3%D8%B3%D8%A9-%D9%83%D9%87%D8%B1%D8%A8%D8%A7-%D9%84%D8%A8%D9%86%D8%A7%D9%86-1793269312</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>الاخبار
+23 تشرين أول 2026
+Beirut
+بيان صادر عن مجلس إدارة مؤسسة كهرباء لبنان
+قرّر مجلس إدارة مؤسسة كهرباء لبنان، في جلسته المنعقدة هذا المساء، قطع التغذية بالتيار الكهربائي عن الإدارات والمؤسسات العامة والمصالح المستقلة، بما فيها مصالح المياه، التي تخلّفت عن تسديد مستحقاتها لمؤسسة كهرباء لبنان رغم الإنذارات المتكررة الموجّهة إليها، باستثناء المستشفيات الحكومية، وذلك اعتبارًا من صباح يوم الاثنين الواقع فيه ٢ تشرين الثاني ٢٠٢٦.
+وعليه، تُدعى الجهات المعنية إلى تسديد المستحقات المتوجبة عليها قبل الموعد المذكور، تفاديًا لقطع التغذية عنها.
+ويُعتبر هذا البيان بمثابة كتاب تبليغ إلى جميع الجهات المعنية بهذا الإجراء.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:14:38.373520+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | وزارة الطاقة: اجتماعات مكثّفة بين الفريقين اللبناني والقطري ولا تأخير</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101219/%D9%88%D8%B2%D8%A7%D8%B1%D8%A9-%D8%A7%D9%84%D8%B7%D8%A7%D9%82%D8%A9-%D8%A7%D8%AC%D8%AA%D9%85%D8%A7%D8%B9%D8%A7%D8%AA-%D9%85%D9%83%D8%AB-%D9%81%D8%A9-%D8%A8%D9%8A%D9%86-%D8%A7%D9%84%D9%81%D8%B1%D9%8A%D9%82%D9%8A%D9%86-%D8%A7%D9%84%D9%84%D8%A8%D9%86%D8%A7%D9%86%D9%8A-%D9%88%D8%A7%D9%84%D9%82%D8%B7%D8%B1%D9%8A-%D9%88%D9%84%D8%A7-%D8%AA%D8%A3%D8%AE%D9%8A%D8%B1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>وزارة الطاقة: اجتماعات مكثّفة بين الفريقين اللبناني والقطري ولا تأخير
+صدر عن وزارة الطاقة والمياه البيان الآتي: 
+تحاول بعض وسائل الإعلام المعروفة بعلاقاتها المشبوهة، تعكير المسار الايجابي الذي يشهده قطاع الطاقة بعد اعلان دولة قطر الشقيقة عن استعدادها للاستثمار في حلول متنوعة ومستدامة في القطاع. كما تدعي زوراً ان هناك دعوة لوزير الطاقة والمياه جو الصدي وجهت اليه لزيارة قطر وتخلف عنها وانه يتلكأ عن توقيع إتفقاق مع الدوحة.
+دحضاً لهذه الاكاذيب يهمنا ان نؤكد ان:
+*لم توجه اي دعوة رسمية حتى اللحظة للصدي لزيارة قطر.
+*الاجتماعات بين الفريقين التقنيين اللبناني والقطري متواصلة وبشكل مكثف منذ أكثر من أسبوعين في بيروت والاسبوع المقبل ستستأنف الاجتماعات بين الفريقين في الدوحة.
+*عند التوصل الى اعلان نوايا، سيرفع الى مجلس الوزراء للموافقة عليه.
+يمكن لكل وسائل الاعلام الاستيضاح عن صحة أي معلومة قبل نشرها، لكن للأسف بعض الأقلام الصفراء المجندة من بعض الاطراف التي اغرقت لبنان بالعتمة، يستفذها ان يوضع لبنان على سكة التعافي الكهربائي بعد سنوات من الاخفاقات. 
+فحمى الله لبنان من تجار الكلمة.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:14:44.345855+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | الصدي يلتقي النائبة نجاة عون ووفداً من بلدية النبطية</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101218/%D8%A7%D9%84%D8%B5%D8%AF%D9%8A-%D9%8A%D9%84%D8%AA%D9%82%D9%8A-%D8%A7%D9%84%D9%86%D8%A7%D8%A6%D8%A8%D8%A9-%D9%86%D8%AC%D8%A7%D8%A9-%D8%B9%D9%88%D9%86-%D9%88%D9%88%D9%81%D8%AF%D8%A7-%D9%85%D9%86-%D8%A8%D9%84%D8%AF%D9%8A%D8%A9-%D8%A7%D9%84%D9%86%D8%A8%D8%B7%D9%8A%D8%A9</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>الاخبار
+22 تشرين أول 2026
+Beirut
+الصدي يلتقي النائبة نجاة عون ووفداً من بلدية النبطية
+التقى وزير الطاقة والمياه جو الصدي النائبة نجاة عون لحضور مدير عام مؤسسة مياه بيروت وجبل لبنان المهندس ربيع خليفة وتناول البحث موضوع الصرف الصحي.
+كما بحث مع نائب رئيس بلدية مدينة النبطية محمد عبد الأمير حجازي على رأس وفد بلدي شؤون الطاقة في المدينة.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:14:50.587117+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | مشروع مشترك بقيمة 19.5 مليون يورو لتعزيز خدمات إمدادات المياه في لبنان</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101217/%D9%85%D8%B4%D8%B1%D9%88%D8%B9-%D9%85%D8%B4%D8%AA%D8%B1%D9%83-%D8%A8%D9%82%D9%8A%D9%85%D8%A9-195-%D9%85%D9%84%D9%8A%D9%88%D9%86-%D9%8A%D9%88%D8%B1%D9%88-%D9%84%D8%AA%D8%B9%D8%B2%D9%8A%D8%B2-%D8%AE%D8%AF%D9%85%D8%A7%D8%AA-%D8%A5%D9%85%D8%AF%D8%A7%D8%AF%D8%A7%D8%AA-%D8%A7%D9%84%D9%85%D9%8A%D8%A7%D9%87-%D9%81%D9%8A-%D9%84%D8%A8%D9%86%D8%A7%D9%86</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>مشروع مشترك بقيمة 19.5 مليون يورو لتعزيز خدمات إمدادات المياه في لبنان
+الصدي: يدعم جهود إصلاح قطاع المياه وتعزيز كفاءة الخدمات وحماية الموارد المائية
+أكد وزير الطاقة والمياه جو الصدي أن مشروع "تعزيز إدارة الموارد المائية – المرحلة الإضافية " (WAMA+) المموَّل من الاتحاد الأوروبي وألمانيا، وتنفّذه الوكالة الألمانية للتعاون الدولي (GIZ)بالشراكة مع وزارة الطاقة والمياه ومؤسسات المياه الأربع، يدعم جهود إصلاح قطاع المياه في لبنان وتعزيز كفاءة تقديم خدمات المياه العامة وحماية الموارد المائية وكذلك سيساهم بتحسينات ملموسة وقابلة للقياس في أداء مؤسسات المياه.
+وإذ شكر الاتحاد الأوروبي والحكومة الألمانية على الدعم المتواصل لقطاع المياه،
+أشار خلال حفل إطلاق المشروع الذي أقيم في الوزارة الى ان هذا المشروع يتكامل مع استراتيجية التحول الرقمي للوزارة ومؤسسات المياه. أردف: "تنفيذه سيساهم في دمج أنظمة المراقبة ومعلومات المشتركين ضمن إطار رقمي متكامل ومنسجم، يستند إلى معايير موحّدة للبيانات ومسؤوليات واضحة في ما يتعلق بصيانة المعلومات وتحديثها".
+أضاف: "يشكّل إطلاق المشروع اليوم خطوةً متقدمة لمعالجة افتقار مؤسسات المياه العامة إلى بيانات موثوقة ومتكاملة. كما يسهم بتحقيق أولويتين تتشاركان فيهما الوزارة ومؤسسات المياه الأربع، وهما: مراقبة مصادر المياه العامة من خلال أنظمة التحكم الإشرافي وجمع البيانات (SCADA)، وتحديث قاعدة بيانات المشتركين التي تضم 800 ألف مشترك. سيصبح بإمكان مؤسسات المياه تحديد المشكلات التشغيلية، والتحكم في الإمدادات بصورة أكثر فاعلية، وتخصيص الموارد على أسس أكثر موثوقية".
+ختم الصدي: "من خلال تحسين الرقابة على الإنتاج والتكاليف التشغيلية، وتعزيز الفوترة وتحصيل الإيرادات، ستسهم هاتان الركيزتان بشكل مباشر في تعزيز الاستدامة المالية لمؤسسات المياه".
+من جانبه، قال السفير الألماني لدى لبنان السيد توماس تسانايزن: "كانت ألمانيا والاتحاد الأوروبي أبرز الجهات المساهمة في دعم قطاع المياه في لبنان خلال السنوات الأخيرة. ومن خلال هذا المشروع المشترك، نعمل على تعزيز قدرات المؤسسات العامة، وتشجيع اعتماد تعرفة عادلة وشفافة، وتحسين إمكانية الوصول إلى البيانات، بما يسهم في تحسين إدارة الموارد المائية بشكل عام. وتهدف شراكتنا الثلاثية، التي تجمع لبنان وألمانيا والاتحاد الأوروبي، إلى أن ينعم الجميع في لبنان بإمكانية وصول أفضل إلى المياه، باعتبارها حقاً أساسياً من حقوق الإنسان".
+بدور، أكّد السيد سامي السعدي، نائب رئيس بعثة الاتحاد الأوروبي لدى لبنان، أن "الاتحاد الأوروبي يتطلع إلى إحراز تقدم ملموس في تنفيذ إصلاحات قطاع المياه، بما يتماشى مع الاستراتيجية الوطنية لقطاع المياه. فتحقيق نتائج مستدامة يتطلب ملكية مؤسسية راسخة، وتحديداً واضحاً للمسؤوليات، والتزاماً مستمراً من جميع الجهات المعنية".
+أضاف: "انّ تعيين فريق مؤهل ومتفرّغ لقيادة تنفيذ مشروع WAMA+ في الوقت المناسب أمراً أساسياً، إذ يساعد على ضمان التنسيق الفعّال واستمرارية العمل وتحقيق النتائج المرجوّة، بالتوازي مع وضع الأسس اللازمة لاستدامة المشروع على المدى الطويل".
+سيساهم المشروع في تعزيز الكفاءة التشغيلية لمؤسسات المياه الإقليمية، والمساءلة العامة، وتحسين إدارة الإيرادات، من خلال تحسين توفّر البيانات التي تدعم اتخاذ قرارات شفافة ومستندة إلى الأدلة. ويستمر المشروع حتى منتصف عام 2029، بتمويل من الاتحاد الأوروبي قدره 16.7 مليون يورو، ومساهمة ألمانية تبلغ 2.8 مليون يورو، ليصل إجمالي التمويل إلى 19.5 مليون يورو.
+وعلى مدى السنوات الثلاث المقبلة، سيدعم المشروع مؤسسات المياه الإقليمية في اعتماد أنظمة رقمية لقياس ومراقبة إنتاج المياه في 400 مصدر رئيسي للمياه، وتحديث بيانات نحو 800,000 مشترك في خدمات المياه، من خلال خدمات رقمية للمشتركين.
+كما سيساعد المشروع مؤسسات المياه على تقديم خدمات أكثر شفافية، والحدّ من من الفاقد المائي بوتيرة أسرع، وتوسيع قاعدة المشتركين، وإصدار فواتير تعكس الاستهلاك الفعلي للمياه، فضلاً عن التخطيط للاستثمارات المستقبلية استناداً إلى بيانات موثوقة.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:14:56.740550+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | كتب وزير الطاقة والمياه جو الصدي عبر حسابه على منصة X:</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101216/%D9%83%D8%AA%D8%A8-%D9%88%D8%B2%D9%8A%D8%B1-%D8%A7%D9%84%D8%B7%D8%A7%D9%82%D8%A9-%D9%88%D8%A7%D9%84%D9%85%D9%8A%D8%A7%D9%87-%D8%AC%D9%88-%D8%A7%D9%84%D8%B5%D8%AF%D9%8A-%D8%B9%D8%A8%D8%B1-%D8%AD%D8%B3%D8%A7%D8%A8%D9%87-%D8%B9%D9%84%D9%89-%D9%85%D9%86%D8%B5%D8%A9-X-1792747636</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>الاخبار
+16 تشرين أول 2026
+Beirut
+كتب وزير الطاقة والمياه جو الصدي عبر حسابه على منصة X:
+كتب وزير الطاقة والمياه جو الصدي عبر حسابه على منصة X:
+تتويجاً لمسار عمل دؤوب بدأناه مع دولة قطر منذ أشهر، جاء إعلان اليوم عن مقاربة متكاملة لبناء وتشغيل البنى التحتية الكهربائية في لبنان، بما يشكّل حلاً مستداماً للقطاع على المدى المتوسط والبعيد، وسنستمر بالعمل معاً لاستكمال الخطوات المتبقية في المرحلة القادمة.
+أما معالجة الأزمة الآنية، فتبقى مسؤولية الحكومة مجتمعة، والمطلوب التجاوب مع مساعينا، وتسديد فواتير القطاع العام المتوجبة، وتعويض إعفاءات الجنوب، واقرار التعرفة المتحركة لتأمين الفيول وضمان استمرار وزيادة التغذية الكهربائية وتخفيف الأكلاف على المواطنين خلال الأشهر المقبلة.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:15:02.868664+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | إلتقى وزير الطاقة والمياه جو الصدي سفير اليابان في لبنان كنجي يوكوتا (Kenji Yokota)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101215/%D8%A5%D9%84%D8%AA%D9%82%D9%89-%D9%88%D8%B2%D9%8A%D8%B1-%D8%A7%D9%84%D8%B7%D8%A7%D9%82%D8%A9-%D9%88%D8%A7%D9%84%D9%85%D9%8A%D8%A7%D9%87-%D8%AC%D9%88-%D8%A7%D9%84%D8%B5%D8%AF%D9%8A-%D8%B3%D9%81%D9%8A%D8%B1-%D8%A7%D9%84%D9%8A%D8%A7%D8%A8%D8%A7%D9%86-%D9%81%D9%8A-%D9%84%D8%A8%D9%86%D8%A7%D9%86-%D9%83%D9%86%D8%AC%D9%8A-%D9%8A%D9%88%D9%83%D9%88%D8%AA%D8%A7-Kenji-Yokota</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>الاخبار
+14 تشرين أول 2026
+Beirut
+إلتقى وزير الطاقة والمياه جو الصدي سفير اليابان في لبنان كنجي يوكوتا (Kenji Yokota)
+إلتقى وزير الطاقة والمياه جو الصدي سفير اليابان في لبنان كنجي يوكوتا (Kenji Yokota) وتناول البحث العلاقة الثنائية بين البلدين والتعاون تحديداً في قطاعي الطاقة والمياه.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:15:09.052657+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | "الطاقة": حصر أسباب إعتكاف الوزير بالمتأخرات كذب وتضليل</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101214/%D8%A7%D9%84%D8%B7%D8%A7%D9%82%D8%A9-%D8%AD%D8%B5%D8%B1-%D8%A3%D8%B3%D8%A8%D8%A7%D8%A8-%D8%A5%D8%B9%D8%AA%D9%83%D8%A7%D9%81-%D8%A7%D9%84%D9%88%D8%B2%D9%8A%D8%B1-%D8%A8%D8%A7%D9%84%D9%85%D8%AA%D8%A3%D8%AE%D8%B1%D8%A7%D8%AA-%D9%83%D8%B0%D8%A8-%D9%88%D8%AA%D8%B6%D9%84%D9%8A%D9%84</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>صدر عن المكتب الإعلامي لوزير الطاقة والمياه جو الصدي البيان الآتي:
+طالعتنا صحيفة "الاخبار" بمقال بتاريخ ١٤/١٠/٢٠٢٦ حمل عنوان: "حجّة متأخرات الإدارات والمؤسسات العامة لا تغطّي الفشل: لماذا يعتكف وزير الطاقة؟". صحيح ان مصداقية الاخبار تعرف من موقع نشرها وأن مجرد ذكر "الأخبار" يكفي لضرب مصداقية اي خبر، لكننا نكتفي بالتذكير أن:
+*حصر أسباب إعتكاف الوزير جو الصدي فقط بمتأخرات الوزارات الإدارات والمؤسسات العامة، هو تضليل وتزوير للحقائق. فهناك ٤ مترتبات محقة على عاتق مجلس الوزراء وهي الى جانب المتأخرات: إعتماد تعرفة متحركة لسعر الكهرباء (وهي خطوة إصلاحية مطلوبة من لبنان)، تسديد الدولة لإعفاءات الجنوب وتسديدها ايضاً لكلفة التصليحات في الجنوب. 
+* رفض الوزير الصدي منذ اللحظة الاولى الاستمرار بنهج مراكمة الديون على لبنان لتأمين بضع ساعات من الكهرباء والذي كبّدنا مليارات الدولارات وهي عملياً من جيوب المودعين وساهمة بالانهيار المالي الذي وصل اليه لبنان. لذا رفض إستمرار مراكمة الديون للسير بالعقد العراقي، بعدما تخطى حجم الاستدانة مليار و٢١٥ مليون دولار، فيما شجع مؤسسة كهرباء لبنان على حصولها على كميات من المحروقات وفق العقد بشرط تسديد ثمنها من جبايتها.
+*بدوره، الجانب العراقي وجّه عبر شركة SOMO العراقية كتابين لوزارة الطاقة رقم ١٣٦١٧ تاريخ ١٦/٦/٢٠٢٥ ورقم ١٧٨٤٨ تاريخ ٤/٨/٢٠٢٥، أعلن بموجبهما إيقاف تجهيز وزارة الطاقة والمياه بمنتوج زيت الوقود لحين تقديم آلية محكمة لتقييد الشحنات التي تجاوزت مدة استحقاقها سنوات عدة.
+في الختام، تعمٌد "الأخبار" تشويه خلفيات الاعتكاف لن يغير حقيقة ان على الحكومة تحمّل مسؤولياتها في النقاط الأربعة المحقة ولن ينطلي على اللبنانيين الذين صارحهم الوزير الصدي بشكل لا لبس فيه بهذه الأسباب خلال مؤتمره الصحافي في ٦/١٠/٢٠٢٦ لإعلان الاعتكاف.
+فحمى الله لبنان من "تجار الكلمة".</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:15:15.059130+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | لقاءات للصدي مع وفود مناطقية ومجلس الادارة الجديد لـ"الليطاني"</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101213/%D9%84%D9%82%D8%A7-%D8%A7%D8%AA-%D9%84%D9%84%D8%B5%D8%AF%D9%8A-%D9%85%D8%B9-%D9%88%D9%81%D9%88%D8%AF-%D9%85%D9%86%D8%A7%D8%B7%D9%82%D9%8A%D8%A9-%D9%88%D9%85%D8%AC%D9%84%D8%B3-%D8%A7%D9%84%D8%A7%D8%AF%D8%A7%D8%B1%D8%A9-%D8%A7%D9%84%D8%AC%D8%AF%D9%8A%D8%AF-%D9%84%D9%80-%D8%A7%D9%84%D9%84%D9%8A%D8%B7%D8%A7%D9%86%D9%8A</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>الاخبار
+13 تشرين أول 2026
+Beirut
+لقاءات للصدي مع وفود مناطقية ومجلس الادارة الجديد لـ"الليطاني"
+إلتقى وزير الطاقة والمياه جو الصدي مجلس الإدارة الجديد للمصلحة الوطنية لنهر الليطاني برئاسة رئيس مجلس الإدارة – المدير العام د. سامي علوية حيث أعطاهم توجهاته بضرروة تعزيز الشفافية والحوكمة الرشيدة وبذل كل الجهود لخدمة المواطنين والعمل على تأمين الاستدامة المالية.
+كما ترأس اجتماع عمل حول واقع المياه في قضاء الكورة بحضور النائب فادي كرم، المدير العام لمؤسسة مياه لبنان الشمالي خالد عبيد وعدد من أعضاء مجلس الإدارة.
+كذلك عرض شؤون الطاقة والمياه والصرف الصحي مع وفد بلدي ضم: رئيس يلدية الجديدة -البوشرية- السد أوغيست باخوس، رئيس بلدية الفنار ميشال سلامة، رئيس بلدية رومية حنا زينون، رئيس بليدة عين سعادة موريس اسمر ورئيس بلدية المنصورية فؤاد الحاج.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:15:21.075360+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | إستقبل وزير الطاقة والمياه جو الصدي السفير الألماني الجديد</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101212/%D8%A5%D8%B3%D8%AA%D9%82%D8%A8%D9%84-%D9%88%D8%B2%D9%8A%D8%B1-%D8%A7%D9%84%D8%B7%D8%A7%D9%82%D8%A9-%D9%88%D8%A7%D9%84%D9%85%D9%8A%D8%A7%D9%87-%D8%AC%D9%88-%D8%A7%D9%84%D8%B5%D8%AF%D9%8A-%D8%A7%D9%84%D8%B3%D9%81%D9%8A%D8%B1-%D8%A7%D9%84%D8%A3%D9%84%D9%85%D8%A7%D9%86%D9%8A-%D8%A7%D9%84%D8%AC%D8%AF%D9%8A%D8%AF</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>الاخبار
+13 تشرين أول 2026
+Beirut
+إستقبل وزير الطاقة والمياه جو الصدي السفير الألماني الجديد
+إستقبل وزير الطاقة والمياه جو الصدي السفير الألماني الجديد في لبنان توماس تسانايزن (Thomas ZAHNEISEN) في لقاء تعارفي وكانت فرصة لعرض المشاريع المرتبطة بقطاعات الوزارة والتي تساهم بها ألمانيا وسبل تعزيز العلاقة بين البلدين.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:15:27.210240+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | بيان صادر عن مجلس إدارة مؤسسة كهرباء لبنان</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101211/%D8%A8%D9%8A%D8%A7%D9%86-%D8%B5%D8%A7%D8%AF%D8%B1-%D8%B9%D9%86-%D9%85%D8%AC%D9%84%D8%B3-%D8%A5%D8%AF%D8%A7%D8%B1%D8%A9-%D9%85%D8%A4%D8%B3%D8%B3%D8%A9-%D9%83%D9%87%D8%B1%D8%A8%D8%A7-%D9%84%D8%A8%D9%86%D8%A7%D9%86</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>عقد مجلس إدارة مؤسسة كهرباء لبنان اجتماعه بعد ظهر اليوم، الاثنين 12 تشرين الأول 2026، وناقش عدداً من الملفات المتعلقة بعمل المؤسسة، ولا سيما ملف إعادة تشغيل معملي الزوق والجية.
+وثمّن المجلس دور وسائل الإعلام في مواكبة جهوده ومساندته لتخطّي المصاعب وزيادة الإنتاج الكهربائي، والمساهمة في إنجاح مهمة مجلس الإدارة الجديد خدمةً للمصلحة العامة.
+ودعا المجلس وسائل الإعلام إلى توخّي الدقة في نقل المعلومات المتعلقة بملفات المؤسسة، مشدداً على أنّ مجلس إدارتها هو المرجع الرسمي الوحيد للمعلومات الصادرة عنها.
+كما دعا إلى إبعاد المجلس وملفات المؤسسة عن التجاذبات السياسية والمصالح الشخصية، وإلى إخراج ملف إعادة تشغيل المعملين من السجالات الإعلامية، إفساحاً للمجال أمام معالجته ضمن الأطر المؤسسية المختصة، خدمةً للمصلحة العامة.
+وفي سياق مناقشة هذا الملف، أكّد المجلس تضامنه الكامل مع عضوَي اللجنة المكلّفَين بدراسة إمكانية إعادة تشغيل معملي الزوق والجية، موضحاً أنّ إعداد هذا التقرير أُسند إليهما رسمياً بقرار من مجلس الإدارة، في إطار المهمة الموكلة إليهما.
+وبعد التداول، اتخذ مجلس الإدارة القرار الآتي:
+بعد الاطلاع على العرض النهائي للجنة المكلّفة بدراسة إعادة تشغيل معملي الزوق والجية، وعلى القرارات القضائية ذات الصلة ومقتضيات الخبرة القضائية الجارية لدى مجلس شورى الدولة، وبعد المناقشة، وحرصاً على المصلحة العامة وزيادة إنتاج الكهرباء وتخفيف الأعباء عن المواطنين وصون المال العام، قرّر مجلس الإدارة ما يأتي:
+أولاً: الموافقة المبدئية على إعادة تشغيل المعملين. ويجري التحضير لإعادة تشغيل الوحدات التي تثبت سلامتها وجاهزيتها، على أن يبدأ تشغيل كل وحدة بعد توثيق نتائج الكشوف والفحوص من الجهة الصانعة MAN.
+ثانياً: تنفيذ الإجراءات بالتنسيق مع الجهات المعنية، مع مراعاة النزاعات القضائية القائمة، ولا سيما أمام مجلس شورى الدولة، والتقيّد بالقرارات القضائية ذات الصلة، دون المسّ بهذه النزاعات أو استباق نتائجها، ومع حفظ حقوق جميع الفرقاء. وتكلّف الدائرة القانونية، بالتنسيق مع وكيل المؤسسة، بالتحقّق من مقتضيات القرارات والتدابير النافذة، وبمتابعة الخبرة القضائية والتنسيق مع الخبير ضمن مهمته. وقبل أي تشغيل أو تفكيك أو صيانة أو استبدال قطع من شأنه التأثير في موضوع الخبرة، توثّق الحالة الفنية وتحفظ الأدلة والقطع.
+ثالثاً: التأكيد أن إعادة التشغيل والإجراءات المرتبطة بها لا تشكّل إبراءً لذمة المشغّل، صراحةً أو ضمناً، ولا إعفاءً له من أي التزامات أو مسؤوليات، وتبقى حقوق المؤسسة ومطالباتها تجاهه محفوظة كاملةً، مع التقيّد بما تقضي به الأحكام القضائية النهائية. ولا يشكّل الكشف أو الصيانة أو إعادة التشغيل إقراراً بسلامة الأعمال السابقة أو بصحة المطالبات المتنازع عليها، أو قبولاً بقطع الغيار محل النزاع، أو تنازلاً عن حقوق المؤسسة تجاه أي جهة معنية. وتتخذ بالتوازي الإجراءات اللازمة لحفظ المطالبات والكفالات والضمانات والمهل القانونية والتعاقدية، دون انتظار انتهاء الخبرة أو صدور الحكم.
+رابعاً: تكليف اللجنة بالاستعانة بكافة الخبرات الفنية اللازمة للكشف، سيما الجهة الصانعة MAN – Everllence، على مجموعات التوليد وتجهيزات المعملين، وتحديد حالتها وجاهزيتها، ووضع خطة واضحة للأعمال والفحوص اللازمة قبل التشغيل ولمراحله وخطواته المتتابعة، ورفعها إلى مجلس الإدارة لاتخاذ القرارات اللازمة تباعاً. وتشمل الخطة تحديد الوحدات المقترح تشغيلها، والفحوص والأعمال المطلوبة لكل وحدة، وتسلسل التنفيذ ومداه وكلفته والجهات المسؤولة عنه.
+خامساً: فصل كافة الكشوف والصيانة والتشغيل الجديدة عن المطالبات السابقة محل النزاع. ولا يجيز هذا القرار تسوية تلك المطالبات أو إقرارها أو تسديدها أو إعطاء دفعة على حسابها، ولا التنازل عن أي حق أو كفالة أو ضمان. وتُعرض التعاقدات والنفقات اللازمة لإعادة التشغيل على مجلس الإدارة لاعتمادها وفق الأصول القانونية والتعاقدية.</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:15:33.242408+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | ورقة سياسة قطاع الكهرباء, تنظيم الفطاع، إلاطار الانتقالي والنموذج طويل الامد 21/تموز/2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101159/%D9%88%D8%B1%D9%82%D8%A9-%D8%B3%D9%8A%D8%A7%D8%B3%D8%A9-%D9%82%D8%B7%D8%A7%D8%B9-%D8%A7%D9%84%D9%83%D9%87%D8%B1%D8%A8%D8%A7-%D8%AA%D9%86%D8%B8%D9%8A%D9%85-%D8%A7%D9%84%D9%81%D8%B7%D8%A7%D8%B9-%D8%A5%D9%84%D8%A7%D8%B7%D8%A7%D8%B1-%D8%A7%D9%84%D8%A7%D9%86%D8%AA%D9%82%D8%A7%D9%84%D9%8A-%D9%88%D8%A7%D9%84%D9%86%D9%85%D9%88%D8%B0%D8%AC-%D8%B7%D9%88%D9%8A%D9%84-%D8%A7%D9%84%D8%A7%D9%85%D8%AF-21-%D8%AA%D9%85%D9%88%D8%B2-2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ورقة سياسة قطاع الكهرباء, تنظيم الفطاع، إلاطار الانتقالي والنموذج طويل الامد 21/تموز/2026
+مرفق ربطا ورقة سياسة قطاع الكهرباء, تنظيم الفطاع، إلاطار الانتقالي والنموذج طويل الامد 21/تموز/2026 باللغتين العربي والانكلزي
+- المشاريع
+- مشاريع الوزارة
+- السدود الوطنية
+- الشراكة والبرامج
+- الشراكة والبرامج
+- الشركاء
+- العمل مع الوزارة
+- تصنيف
+- Register your Business
+- هل تعلم؟
+- المياه
+- كهرباء
+- توفير الطاقة
+- النفط
+- المعاملات والخدمات
+- معاملات وارشادات
+- القوانين و الأنظمة
+- النماذج
+- أسئلة وأجوبة
+- مواقع مفيدة</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:15:39.418864+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Ministry_of_Energy_and_Water.xlsx
+++ b/Ministry_of_Energy_and_Water.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4671,6 +4671,293 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | تدشين نظام SCADA في مؤسسة مياه لبنان الجنوبي بالشراكة مع اللجنة الدولية للصليب الأحمر</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101210/%D8%AA%D8%AF%D8%B4%D9%8A%D9%86-%D9%86%D8%B8%D8%A7%D9%85-SCADA-%D9%81%D9%8A-%D9%85%D8%A4%D8%B3%D8%B3%D8%A9-%D9%85%D9%8A%D8%A7%D9%87-%D9%84%D8%A8%D9%86%D8%A7%D9%86-%D8%A7%D9%84%D8%AC%D9%86%D9%88%D8%A8%D9%8A-%D8%A8%D8%A7%D9%84%D8%B4%D8%B1%D8%A7%D9%83%D8%A9-%D9%85%D8%B9-%D8%A7%D9%84%D9%84%D8%AC%D9%86%D8%A9-%D8%A7%D9%84%D8%AF%D9%88%D9%84%D9%8A%D8%A9-%D9%84%D9%84%D8%B5%D9%84%D9%8A%D8%A8-%D8%A7%D9%84%D8%A3%D8%AD%D9%85%D8%B1</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>الصدي: همنا تقديم خدمة أفضل للمواطنين وضمان إمدادات مياه أكثر انتظاماً وموثوقية
+برعاية وحضور  وزير الطاقة والمياه جو الصدي، دشّنت مؤسسة مياه لبنان الجنوبي اليوم مشروع «نظام التحكم والإدارة المركزي – سكادا»، الذي تضمن أعمال تطوير وتأهيل مركز التحكم والإدارة المركزي والمكاتب الإدارية، ومرافق الطاقة والخوادم والتجهيزات التشغيلية التابعة له.
+تقدّم حضور حفل الافتتاح وزير الطاقة والمياه جو الصدي، وأنييس دور، رئيسة بعثة اللجنة الدولية للصليب الأحمر في لبنان، نائب رئيس مجلس الانماء والإعمار يوسف كرم، أعضاء مجلس إدارة مؤسسة مياه لبنان الجنوبي، وممثلو المنظمات الدولية والمحلية الشريكة.
+استُهلّ حفل الافتتاح بكلمة ترحيبية من مؤسسة مياه لبنان الجنوبي، أعقبها عرض فيديو خاص عن مراحل تطوير وتنفيذ مشروع تأهيل وتطوير «مركز التحكم والإدارة المركزي» وأهميته.
+ثم ألقى راعي الاحتفال كلمة بارك فيها للمؤسسة وللجنة الدولية للصليب الأحمر نجاح هذا المشروع الحيوي، مضيفاً: «يشكّل افتتاح نظام التحكم والمراقبة والادارة المركزي «SCADA» اليوم في مؤسسة مياه لبنان الجنوبي خطوة مهمة لتحديث خدمات المياه وتعزيز قدرة المؤسسة على إدارة مرافقها بكفاءة. لذا نتوجّه بالشكر إلى اللجنة الدولية للصليب الأحمر على مساهمتها من خلال هذه المنحة، وعلى دعمها المستمر لضمان استمرارية خدمات المياه الأساسية في لبنان.
+أضاف: "يتيح هذا النظام متابعة إنتاج المياه وتشغيل المنشآت المرتبطة به بشكل مباشر، ويساعد فرق العمل على اكتشاف الأعطال بسرعة، والتدخّل لمعالجتها، وتقليص فترات توقّف الخدمة"، موضحاً "أنه يساعد كذلك من خلال المراقبة المستمرة على تحسين استهلاك الطاقة، ورصد أي تغيّرات غير طبيعية في تدفّق المياه قد تشير إلى تسرّب أو خلل، وحماية المعدّات وخفض كلفة التشغيل، بما يعزّز الاستدامة المالية للمؤسسة. الهدف الأساسي من هذا الاستثمار هو تقديم خدمة أفضل للمواطنين. ولتحقيق ذلك، من الضروري مواصلة تدريب الموظفين، وصيانة النظام، والاستفادة من المعلومات التي يوفّرها في الإدارة اليومية، لضمان إمدادات مياه أكثر انتظاماً وموثوقية".
+تلت ذلك كلمة السيدة أنييس دور، رئيسة بعثة اللجنة الدولية للصليب الأحمر في لبنان، قالت فيها: «أثبتت الشراكة بين اللجنة الدولية للصليب الأحمر ومؤسسة مياه لبنان الجنوبي أهمّيتها البالغة، خصوصًا خلال النزاع الأخير. وقد أتاحت استجابةً سريعةً وفاعلةً للاحتياجات الملحّة للمجتمعات النازحة والأكثر عرضةً للمخاطر في المناطق المتضرّرة من النزاع والتي يصعب الوصول إليها. واليوم، يعكس افتتاح مركز التحكّم الجديد بنظام “SCADA” التزام اللجنة الدولية بمعالجة الاحتياجات الأساسية على مستوى البنية التحتية وتحسين جودة حياة الأشخاص في جنوب لبنان».
+مدير عام مؤسسة مياه لبنان الجنوبي الدكتور وسيم ضاهر، أكّد في كلمته أنّ «مشروع السكادا يقع في صلب استراتيجية المؤسسة لتحقيق استمرارية التغذية بمياه الشرب، والحفاظ على جودتها، وخفض كلفة إنتاجها وتوزيعها، وتحسين الخدمات المقدّمة للمشتركين. وهو يكمّل مشاريع تطوير المصادر والمحطات والشبكات والخزانات والطاقة الشمسية، من خلال تعزيز قدرتنا على متابعة التشغيل، واكتشاف المشكلات مبكراً، وتوجيه أعمال الصيانة والتدخل استناداً إلى معلومات دقيقة، بما ينعكس خدمة أكثر انتظاماً واستجابة أسرع لاحتياجات أهلنا».
+واستحضر ضاهر تضحيات العاملين في المؤسسة، قائلاً: «نستذكر بكل وفاء وإجلال شهداء المؤسسة التسعة عشر الذين ارتقوا خلال أداء عملهم في السنوات الأخيرة. والوفاء لهم مسؤولية نحملها في استمرار العمل، وفي جعل سلامة العاملين وحمايتهم أولوية ملازمة لكل قرار تشغيلي وتطويري». وشدّد على أنّ «الاعتداءات التي طالت منشآت المؤسسة وموظفيها، والأزمات المالية والتشغيلية المتراكمة، تزيد من إصرارنا على حماية استمرارية المياه وتطوير بيئة الخدمات، لأنّ وصول المياه إلى البيوت جزء أساسي من حماية صحة الناس وكرامتهم واستقرارهم». وتوجّه بالشكر إلى اللجنة الدولية للصليب الأحمر وجميع المساهمين في إنجاز المشروع، مثمّناً جهود فرق المؤسسة والتزامها بمواصلة الخدمة رغم التحديات.
+والجدير ذكره أنّ تطوير وتأهيل «مركز التحكم والإدارة المركزي»، المنفّذ بالتعاون والشراكة مع اللجنة الدولية للصليب الأحمر، يعزّز البنية التقنية والتشغيلية اللازمة لمراقبة محطات المياه والآبار المرتبطة بنظام «سكادا» والتحكم بها عن بُعد، وجمع بيانات التشغيل ومتابعة التنبيهات والأعطال. ويساهم المشروع في تحسين تنظيم الضخ واستخدام المياه والطاقة، وتسريع الاستجابة الفنية وتقليل فترات التوقف، كما يطوّر قدرات المؤسسة على التخطيط للصيانة وإدارة منشآتها واتخاذ القرارات المبنية على المعطيات، بما يدعم استمرارية التغذية بالمياه وكفاءة الخدمة المقدّمة للمواطنين.</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:18:53.887934+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | بيان صادر عن رئيس وأعضاء مجلس إدارة مؤسسة كهرباء لبنان</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101209/%D8%A8%D9%8A%D8%A7%D9%86-%D8%B5%D8%A7%D8%AF%D8%B1-%D8%B9%D9%86-%D8%B1%D8%A6%D9%8A%D8%B3-%D9%88%D8%A3%D8%B9%D8%B6%D8%A7-%D9%85%D8%AC%D9%84%D8%B3-%D8%A5%D8%AF%D8%A7%D8%B1%D8%A9-%D9%85%D8%A4%D8%B3%D8%B3%D8%A9-%D9%83%D9%87%D8%B1%D8%A8%D8%A7-%D9%84%D8%A8%D9%86%D8%A7%D9%86</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>عطفاً على ما أُثير خلال جلسة اللجنة النيابية المختصة بالأشغال العامة والطاقة بشأن إعادة تشغيل معملي الزوق والجية، وعلى التصريحات الإعلامية التي أعقبتها، يهمّ رئيس وأعضاء مجلس إدارة مؤسسة كهرباء لبنان توضيح الآتي:
+أولاً: إنّ ما جرى تداوله بشأن وجود انقسام داخل مجلس الإدارة حول إعادة تشغيل المعملين لا يعكس الواقع. ويؤكد المجلس أنّ رئيسه وأعضاءه يواصلون أداء مهامهم بروح التعاون والمسؤولية المؤسسية، انطلاقاً من الحرص على مصلحة المؤسسة وحسن سير المرفق العام.
+ثانياً: إنّ تحميل أعضاء مجلس الإدارة مسبقاً مسؤولية شخصية عن أي عطل فني قد يطرأ بعد إعادة التشغيل يتجاهل توزيع الصلاحيات والالتزامات بين الجهات المعنية. فالمسؤوليات تُحدَّد وفقاً للقوانين والأنظمة والعقود، وفي ضوء الوقائع والأسباب الفنية، ولا تترتب تلقائياً لمجرد اتخاذ قرار بإعادة التشغيل.
+ثالثاً: قدّم عضو مجلس الإدارة المكلّف بمتابعة الملف المهندس سامر حسنية، عرضاً تقنياً مفصّلاً استند إلى المستندات والمعطيات الواردة من إدارة المؤسسة وشركة MEP. كما أوضح أنّ تقرير اللجنة المكلّفة متابعة الملف سيُعرض على مجلس الإدارة يوم الاثنين المقبل، لدراسته واتخاذ القرار المناسب في ضوء نتائجه. وعليه، فإنّ استباق قرار المجلس أو تحميله تبعات تشغيلية قبل استكمال دراسة الملف يفتقر إلى الأسس اللازمة لتقييمه بصورة موضوعية.
+رابعاً: يسعى المجلس، منذ اليوم الأول لتولّيه مهامه، إلى زيادة إنتاج الكهرباء وتحسين التغذية، بما يخفّف عن اللبنانيين أعباء الاشتراك بالمولدات الخاصة. ويعمل لهذه الغاية على إعادة تشغيل معامل المؤسسة القائمة والاستفادة من قدراتها الإنتاجية، استناداً إلى التقييمات الفنية ومتطلبات السلامة والجدوى التشغيلية.
+وتتولى الجهات المختصة والمشغّل تنفيذ أعمال التشغيل والاضطلاع بالمسؤوليات الفنية المرتبطة بها، كلٌّ ضمن صلاحياته والتزاماته، فيما يمارس مجلس الإدارة صلاحياته التقريرية والرقابية وفقاً للأصول، واضعاً سلامة المنشآت وحسن سير المرفق العام في مقدمة أولوياته.
+خامساً: يؤكد المجلس أنّه يواجه محاولات عرقلة من جهات داخل المؤسسة وخارجها، لغايات لا تخدم المصلحة العامة، تعوق جهوده لزيادة الإنتاج وممارسة دوره الرقابي. ويشدد على أنّ هذه المحاولات لن تثنيه عن أداء واجباته والعمل على تحسين التغذية الكهربائية وتخفيف الأعباء عن المواطنين.
+ويدعو المجلس إلى تحرّي الدقة والموضوعية في تناول هذا الملف، وعدم استباق نتائج الإجراءات الفنية والإدارية أو إطلاق استنتاجات تشكّك في آليات اتخاذ القرار قبل استكمالها. ويؤكد استمراره في ممارسة صلاحياته واتخاذ قراراته استناداً إلى المعطيات الفنية والقانونية والمصلحة العامة، وفقاً للأصول المرعية الإجراء.
+رئيس وأعضاء مجلس إدارة مؤسسة كهرباء لبنان</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:19:00.212203+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | الصدي يطًلع من مجلس إدارة كهرباء لبنان على جهود لاعادة تشغيل معملي الزوق والجية</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101208/%D8%A7%D9%84%D8%B5%D8%AF%D9%8A-%D9%8A%D8%B7-%D9%84%D8%B9-%D9%85%D9%86-%D9%85%D8%AC%D9%84%D8%B3-%D8%A5%D8%AF%D8%A7%D8%B1%D8%A9-%D9%83%D9%87%D8%B1%D8%A8%D8%A7-%D9%84%D8%A8%D9%86%D8%A7%D9%86-%D8%B9%D9%84%D9%89-%D8%AC%D9%87%D9%88%D8%AF-%D9%84%D8%A7%D8%B9%D8%A7%D8%AF%D8%A9-%D8%AA%D8%B4%D8%BA%D9%8A%D9%84-%D9%85%D8%B9%D9%85%D9%84%D9%8A-%D8%A7%D9%84%D8%B2%D9%88%D9%82-%D9%88%D8%A7%D9%84%D8%AC%D9%8A%D8%A9</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>الاخبار
+08 تشرين أول 2026
+Beirut
+الصدي يطًلع من مجلس إدارة كهرباء لبنان على جهود لاعادة تشغيل معملي الزوق والجية
+عقد وزير الطاقة والمياه جو الصدي إجتماعاً مع رئيس مجلس إدارة مؤسسة كهرباء لبنان المهندس نسيب نصر برفقة عضو مجلس الإدارة المكلف بمتابعة الملف المهندس سامر الحسنية واطلعاه على تفاصيل إجتماع لجنة الاشغال العامة والطاقة والنقل النيابية المخصص لمتابعة ملف تشغيل معملي الزوق والجية وعلى جهود مجلس الادارة لاعادة التشغيل وفق مسارين تقني وإداري بما يوفر نحو ساعة ونصف ساعة تغذية إضافية لمدة شهر ونصف الشهر وفق المحروقات المتوفرة حالياً. كما شدّدا على انه متى تمّ تشغيل المعملين، فأي عطل يكون على عاتق المشغل وفق ما ينص عليه عقد التشغيل المعمول به٠</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:19:06.875334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | الصدي يوقّع اتفاقيتي شراء الطاقة لمشروعين لإنتاج الكهرباء من الطاقة الشمسية</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101207/%D8%A7%D9%84%D8%B5%D8%AF%D9%8A-%D9%8A%D9%88%D9%82-%D8%B9-%D8%A7%D8%AA%D9%81%D8%A7%D9%82%D9%8A%D8%AA%D9%8A-%D8%B4%D8%B1%D8%A7-%D8%A7%D9%84%D8%B7%D8%A7%D9%82%D8%A9-%D9%84%D9%85%D8%B4%D8%B1%D9%88%D8%B9%D9%8A%D9%86-%D9%84%D8%A5%D9%86%D8%AA%D8%A7%D8%AC-%D8%A7%D9%84%D9%83%D9%87%D8%B1%D8%A8%D8%A7-%D9%85%D9%86-%D8%A7%D9%84%D8%B7%D8%A7%D9%82%D8%A9-%D8%A7%D9%84%D8%B4%D9%85%D8%B3%D9%8A%D8%A9</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>في خطوة إضافية على مسار تفعيل مشاريع الطاقة المتجددة المرخّصة في لبنان، وقّع وزير الطاقة والمياه جو الصدي اتفاقيتي شراء الطاقة المعدّلتين (Novated, restated, and amended PPAs) مع كلّ من شركتي .C.D.N وEONE، لاستكمال الإجراءات اللازمة للمضي قدماً في تنفيذ مشروعيهما لإنتاج الكهرباء من الطاقة الشمسية. تندرج الاتفاقيتان ضمن التراخيص الإحدى عشرة الممنوحة لمشاريع إنتاج الكهرباء من الطاقة الشمسية في العام 2022 والتي أعاد الصدي تفعيلها فور تسلمه مهامه.
+الصدي اكد أن استكمال توقيع الاتفاقيات الخاصة بالمشاريع المرخّصة يشكّل خطوة عملية نحو تحويل التراخيص القائمة إلى استثمارات فعلية على الأرض، مشدداً على أن الوزارة ستواصل العمل على استكمال الإجراءات المتعلقة بباقي المشاريع، بالتوازي مع الإصلاحات الجارية في قطاع الكهرباء وتهيئة البيئة التنظيمية والمؤسساتية اللازمة لتطوير مشاريع الطاقة المتجددة واستقطاب المزيد من الاستثمارات.
+يأتي هذا التقدم في إطار الجهود المستمرة لإعادة تحريك الاستثمارات في قطاع إنتاج الكهرباء من مصادر الطاقة المتجددة، وتسريع انتقال المشاريع المرخّصة من الإطار القانوني والتعاقدي إلى مرحلة التنفيذ الفعلي، بما يساهم في زيادة القدرات الإنتاجية، وتنويع مزيج الطاقة، والحدّ من الاعتماد على مصادر الطاقة التقليدية المستوردة.
+تكتسب هذه المشاريع أهمية خاصة في ظل الحاجة إلى استقطاب استثمارات القطاع الخاص في قطاع الكهرباء، وتعزيز دور الطاقة المتجددة كأحد المكونات الأساسية لإصلاح القطاع وتحسين أمن الطاقة في لبنان.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:19:13.193763+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | الصدي يعلن اعتكافه عن جلسات مجلس الوزراء: لن أرضى ان يتحمل المواطن وحده أعباء أزمة الطاقة</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101206/%D8%A7%D9%84%D8%B5%D8%AF%D9%8A-%D9%8A%D8%B9%D9%84%D9%86-%D8%A7%D8%B9%D8%AA%D9%83%D8%A7%D9%81%D9%87-%D8%B9%D9%86-%D8%AC%D9%84%D8%B3%D8%A7%D8%AA-%D9%85%D8%AC%D9%84%D8%B3-%D8%A7%D9%84%D9%88%D8%B2%D8%B1%D8%A7-%D9%84%D9%86-%D8%A3%D8%B1%D8%B6%D9%89-%D8%A7%D9%86-%D9%8A%D8%AA%D8%AD%D9%85%D9%84-%D8%A7%D9%84%D9%85%D9%88%D8%A7%D8%B7%D9%86-%D9%88%D8%AD%D8%AF%D9%87-%D8%A3%D8%B9%D8%A8%D8%A7-%D8%A3%D8%B2%D9%85%D8%A9-%D8%A7%D9%84%D8%B7%D8%A7%D9%82%D8%A9</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>أعلن وزير الطاقة والمياه اعتكافه، في هذه المرحلة، عن حضور جلسات مجلس الوزراء، إلى حين تحمّل الحكومة مسؤولياتها تجاه قطاع الطاقة والتعامل الجدي مع الطروحات المقدمة لضمان استمرارية الكهرباء وحماية المواطنين من أعباء إضافية.
+جاء موقف وزير الطاقة خلال مؤتمر صحافي عقده على وقع تفاقم أزمة المحروقات العالمية، وبعد سلسلة تحذيرات وجهها إلى الحكومة، مؤكداً أنه وضع أمامهم المعطيات المتعلقة بتداعيات الأزمة وقدم مجموعة من الحلول لتأمين استمرارية التغذية الكهربائية وتخفيف الكلفة على المواطنين.
+كما أكد الصدي أن قرار الاعتكاف "ليس تخلياً عن المسؤولية، بل تمسك بها ورفعاً للصوت باسم المواطن اللبناني كي لا يتحمل وحده أعباء أزمة الطاقة العالمية"، مشدداً على أنه سيواصل ممارسة كامل مسؤولياته والعمل على حماية استمرارية المرفق العام وحقوق المواطنين.
+كذلك، استعرض وزير الطاقة الخطوات الإصلاحية التي قامت بها الوزارة منذ توليه مهامه، مشيراً إلى تشكيل الهيئة الناظمة لقطاع الكهرباء تطبيقاً لقانون صدر منذ 24 عاماً ولم يُطبّق، لافتاً إلى أن الهيئة تعمل حالياً على التحضير لإطلاق تراخيص لإنتاج وتوزيع الكهرباء من قبل القطاع الخاص خلال الأشهر المقبلة.
+كما أشار إلى تعيين مجلس إدارة جديد لمؤسسة كهرباء لبنان ومجالس إدارات لمؤسسات المياه، بهدف إعادة تفعيل الإدارة ورفع فعاليتها، إضافة إلى إعادة تنظيم قطاع التوزيع والجباية بالتزامن مع توقف سلفات الخزينة التي كبدت الشعب اللبناني اعباء كثيرة، ضمن مسار إصلاحي يهدف إلى تأمين استدامة الخدمات على المدى البعيد.
+وفي ما يتعلق بالإجراءات المطلوبة لمواجهة أزمة المحروقات، أوضح الوزير أنه طالب بتسديد فواتير الكهرباء المتوجبة على الوزارات والمؤسسات العامة، إلا أن التجاوب،، كان «جزئياً ولمرة واحدة»، متسائلاً: «كيف نطلب من المواطن أن يسدد فاتورته كاملة، فيما مؤسسات الدولة نفسها لا تسدد ما يترتب عليها لنتمكن من شراء الفيول؟».
+هذا وكشف أنه طالب أيضاً الحكومة بتسديد قيمة الفاتورة المترتبة عن دعم المتضررين من الحرب، بما يتيح لمؤسسة كهرباء لبنان شراء الفيول وتأمين التغذية، لكنه قال إن هذا الطلب لم يلقَ أي تجاوب حتى الآن.
+الصدي أشار في هذا السياق إلى أن الحكومة تؤمّن الموازنات اللازمة لوزارة الصحة لتغطية المتضررين والنازحين، فيما لا يتم تأمين كلفة الكهرباء المقدمة لهم، معتبراً أن مؤسسة كهرباء لبنان مؤسسة عامة شأنها شأن المستشفيات الحكومية وسائر مؤسسات الدولة.
+كما لفت الوزير كذلك إلى أن الوزارة طرحت اعتماد تعرفة كهرباء متحركة وهي مطلب إصلاحي، بما يسمح بزيادة ساعات التغذية وتخفيف الكلفة الإجمالية التي يتحملها المواطن، ولا سيما أن كلفة الكهرباء من مؤسسة كهرباء لبنان تبقى أقل من كلفة المولدات الخاصة.
+كذلك، اشار الى ان الوزارة «حذرت وقدمت الأرقام وطرحت الحلول وانتظرت المعالجات»، مشيراً إلى أن الاجتماع الوزاري الأخير لم ينتج عنه أي تجاوب فعلي مع الطروحات المقدمة.
+أضاف: «أنا وزير الطاقة، وأقوم بواجباتي في الوزارة لتطبيق القوانين واحترامها وتأمين تسيير المرفق العام بأقل كلفة وضمان استمرارية الخدمات للمواطن»، معتبراً أن مسؤوليته لا تقتصر على حضور جلسات لمجلس الوزراء لا تعطي قطاع الطاقة الاهتمام الذي تتطلبه المرحلة الحالية والأزمة العالمية.
+كما أكد أن الحكومة مجتمعة مطالبة بتحمل مسؤولياتها تجاه قطاع الطاقة ومصالح اللبنانيين كما تفعل مع قطاعات أخرى، محذراً من أن المواطن هو من سيتحمل في نهاية المطاف كلفة عدم اتخاذ القرارات المطلوبة.
+ختم وزير الطاقة بالتأكيد على أنه سيواصل القيام بمسؤولياته في الوزارة، قائلاً: «ازمة الطاقة بتشعباتها مسؤولية وطنية ولا تقع فقط على عاتق الوزارة ولن أرضى بتجاهل أزمة حذرنا منها وقدمنا لمعالجتها الحلول، فيما المطلوب اليوم هو قرار ومسؤولية»</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:19:19.723262+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | تسعيـرة المولـدات الخاصـة في شهـر ايلول 2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101205/%D8%AA%D8%B3%D8%B9%D9%8A%D9%80%D8%B1%D8%A9-%D8%A7%D9%84%D9%85%D9%88%D9%84%D9%80%D8%AF%D8%A7%D8%AA-%D8%A7%D9%84%D8%AE%D8%A7%D8%B5%D9%80%D8%A9-%D9%81%D9%8A-%D8%B4%D9%87%D9%80%D8%B1-%D8%A7%D9%8A%D9%84%D9%88%D9%84-2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2010-10-14</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>الجـمهـوريـة اللبـنانـيـة
+وزارة الطاقــة والميـاه
+المكتـب الإعلامـي
+وزارة الطاقـة والميـاه تـصـدر تسعيـرة المولـدات الخاصـة في شهـر ايلول 2026
+أعلنت وزارة الطاقة والمياه في بيان صدر عن مكتبها الإعلامي أن السعر العادل لتعرفات المولدات الكهربائية الخاصة من شـهر أيلول هو التالي:
+للمشتركين بالعدادات في المدن 52.840 ل.ل. عن كل كيلواط ساعة.:
+- قدرة 5 أمبير: 385.000 ل.ل. + المقطوعية الشهرية 52.840 ل.ل. عن كل كيلواط ساعة.
+- قدرة 10 أمبير: 685.000 ل.ل. + المقطوعية الشهرية x 52.840 ل.ل. عن كل كيلواط ساعة.
+ للمشتركين بالعدادات في المدن حيث امتداد شبكة التوزيع أكثر من 300 متر أو في القرى على ارتفاع اكثر من ٧٠٠ متر:58.124 ل.ل. عن كل كيلواط ساعة :
+- قدرة 5 أمبير : 385.000 ل.ل. (ثابت) + المقطوعية الشهرية x 58.124 ل.ل. عن كل كيلوواط/ساعة.
+- قدرة 10 أمبير : 685.000 ل.ل. (ثابت) + المقطوعية الشهرية x 58.124 ل.ل. عن كل كيلوواط/ساعة.
+* تضاف 300.000 ل.ل. على الشطر الثابت من تسعيرة العدادات لكل 5 أمبير إضافي.
+وإن هذه التعرفـة مبنية على أساس سعر وسطي لصفيحة المازوت (20 ليتر) في شهر أيلول البالغ 2.675.217. ل.ل. وذلك بعد إحتساب كافة مصاريف وفوائد وأكلاف المولدات بالإضافة إلى هامش ربح جيد لأصحابها، وقد أخذنا بعين الاعتبار وبالتنسيق مع وزارة الاقتصاد والتجارة كلفة توزيع الصفيحة من محطة الوقود ولغاية المولد. وهي تأخذ بعين الاعتبار في إحتساب مكونات اساسية فيها ككلفة الزيوت والفلاتر وتهالك المولد المعدل الوسطي الشهري لسعر الدولار في السوق الموازي الذي بلغ 89.700 ل.ل. وقد صدرت هذه التسعيرة بناءً على الجدول الحسابي المعتمد من قبل وزارة الطاقة منذ تاريخ 14/10/2010؛ وتطبيقاً لقرار مجلس الوزراء رقم 2 الصادر بتاريخ 14/12/2011 في شأن إتخاذ التدابير اللازمة لضبط تسعيرة المولدات الخاصة، وإستناداً إلى آلية التطبيق المشتركة بين الوزارات (الطاقة الداخلية والإقتصاد) المعلن عنها بتاريخ 20/12/2011 والتي حَدّدت مسؤولية وزارة الطاقة والمياه في تعميم تسعيرة المولدات الخاصة إستناداً الى أسعار المازوت في نهاية كل شهر".
+من هنا تدعو وزارة الطاقة والمياه أصحاب المولّدات الى الالتزام بقرار وزارة الاقتصاد والتجارة القاضي بالزامية تركيب العدادات وهي سوف تجري دراسة موثقة بهذا الصدد في الفترة المقبلة وصولاً الى تحديث المعادلة المعتمدة لكي تتناسب أكثر فأكثر مع تقلبات أسعار الصرف والوضع الاقتصادي والاجتماعي للمواطنين مع الأخذ بالاعتبار متطلبات أصحاب المولدات الخاصة.
+كما تعلن وزارة الطاقة والمياه أنها أرسلت إلى وزارتي الداخلية والإقتصاد كُتباً حول تسعيرة شهر أيلول 2026 للقيام بالمقتضى بحسب آلية الضبط المشتركة.
+تلفت وزارة الطاقة والمياه انتباه أصحاب المولدات الخاصة والمواطنين الكرام الى عدم جواز ادخال الاضافات التالية الى التسعيرة التوجيهية الصادرة عن الوزارة:
+- ضريبة على القيمة المضافة غير مبرّرة قانوناً بموجب تسجيل رسمي في مديرية الــTVA في وزارة المالية.
+- رسوم أو مبالغ إضافية تحت اي ذريعة ككلفة صيانة مولّد أو شبكات أو غيره...
+- رسوم إضافية للمواطنين الذين يستخدمون أجهزة الطاقة الشمسية الى جانب المولدات الخاصة.
+وهنا تهيب وزارة الطاقة والمياه بالمعنيين بحماية المستهلك وخاصةً وزارة الاقتصاد والتجارة تشديد الرقابة على حسن تطبيق التسعيرة التوجيهية أعلاه واتخاذ اقصى التدابير بحق المخالفين بمواكبة من وزارة الداخلية والبلديات والقضاء المختص.
+تجدر الاشارة الى أن وزارة الطاقة والمياه ترفق ربطاً جدول تركيب التسعيرة التوجيهية المفصّل وكذلك ستنشر هذا الجدول على الموقع الالكتروني الرسمي: www.energyandwater.gov.lb
+* إنتهــى
+بيـروت فـي 1/10/2026</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:19:21.899426+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | الصدي يبحث في واشنطن الضمانات المالية مع البنك الدولي وIFC وMIGA</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101204/%D8%A7%D9%84%D8%B5%D8%AF%D9%8A-%D9%8A%D8%A8%D8%AD%D8%AB-%D9%81%D9%8A-%D9%88%D8%A7%D8%B4%D9%86%D8%B7%D9%86-%D8%A7%D9%84%D8%B6%D9%85%D8%A7%D9%86%D8%A7%D8%AA-%D8%A7%D9%84%D9%85%D8%A7%D9%84%D9%8A%D8%A9-%D9%85%D8%B9-%D8%A7%D9%84%D8%A8%D9%86%D9%83-%D8%A7%D9%84%D8%AF%D9%88%D9%84%D9%8A-%D9%88IFC-%D9%88MIGA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>الاخبار
+30 أيلول 2026
+Beirut
+الصدي يبحث في واشنطن الضمانات المالية مع البنك الدولي وIFC وMIGA
+أكد وزير الطاقة والمياه جو الصدي من واشنطن أن تطوير قطاع الطاقة في لبنان يتطلب استثمارات من القطاع الخاص أو من دول صديقة، وهؤلاء بحاجة إلى ضمانات مالية، باعتبار أنّ القطاع متعثر منذ فترة طويلة.
+الصدي أوضح لـmtv ان هذا الامر كان مدار بحث خلال سلسلة اجتماعات التي شارك فيها ضمن اللقاءات التي عقدها رئيس الحكومة نواف سلام بحضور وزير المال ياسين جابر مع فريق البنك الدولي ومؤسسة التمويل الدولية (IFC) والوكالة الدولية لضمان الاستثمار (MIGA)، مشيراً الى انه أطلعهم على الإصلاحات التي يقوم بتنفيذها في قطاع الطاقة. 
+أضاف: "بالتأكيد لديهم شروط لتقديم ضمانات ولا سيما من ناحية حوكمة قطاع الكهرباء، تطبيق القانون، تحسين الجباية، معالجة الهدر الفني والتعديات وسائر الخطوات الإصلاحية".</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:19:28.273503+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>الموقع الرسمي لوزارة الطاقة والمياه | الصدي: سأطلب من الحكومة إلغاء رسم الـ300 ألف على المحروقات أو تعليقه</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://www.energyandwater.gov.lb/ar/details/101203/%D8%A7%D9%84%D8%B5%D8%AF%D9%8A-%D8%B3%D8%A3%D8%B7%D9%84%D8%A8-%D9%85%D9%86-%D8%A7%D9%84%D8%AD%D9%83%D9%88%D9%85%D8%A9-%D8%A5%D9%84%D8%BA%D8%A7-%D8%B1%D8%B3%D9%85-%D8%A7%D9%84%D9%80300-%D8%A3%D9%84%D9%81-%D8%B9%D9%84%D9%89-%D8%A7%D9%84%D9%85%D8%AD%D8%B1%D9%88%D9%82%D8%A7%D8%AA-%D8%A3%D9%88-%D8%AA%D8%B9%D9%84%D9%8A%D9%82%D9%87</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>الاخبار
+29 أيلول 2026
+Beirut
+الصدي: سأطلب من الحكومة إلغاء رسم الـ300 ألف على المحروقات أو تعليقه
+كتب وزير الطاقة والمياه جو الصدي عبر حسابه على منصة X:
+الأولوية اليوم هي للمواطن وقدرته على تحمّل الأعباء، فلا يجوز تحميله المزيد في ظل الارتفاع الكبير في أسعار النفط عالمياً وانعكاساته محلياً.
+لذلك، سأطلب في جلسة مجلس الوزراء الخميس إلغاء رسم الـ300 ألف على المحروقات او في الحد الأدنى تعليقه، خصوصاً أننا اعترضنا عليه منذ البداية.
+المطلوب اليوم هو التخفيف عن المواطنين.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:19:34.815054+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Ministry_of_Energy_and_Water.xlsx
+++ b/Ministry_of_Energy_and_Water.xlsx
@@ -414,7 +414,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E124"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
